--- a/data/trans_orig/Q24D_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q24D_2-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de veces que han intentado dejar de fumar</t>
+          <t>Número medio de veces que han intentado dejar de fumar (tasa de respuesta: 91,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,21</t>
+          <t>2,02; 3,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,52</t>
+          <t>2,52; 3,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 2,93</t>
+          <t>2,12; 2,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,73</t>
+          <t>2,06; 2,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,15</t>
+          <t>1,57; 2,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,63</t>
+          <t>2,45; 3,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,23</t>
+          <t>2,08; 3,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,82</t>
+          <t>2,15; 2,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,93</t>
+          <t>1,96; 2,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,35</t>
+          <t>2,59; 3,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,83</t>
+          <t>2,18; 2,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,6</t>
+          <t>2,14; 2,62</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,74</t>
+          <t>2,22; 3,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,7</t>
+          <t>2,25; 3,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 2,83</t>
+          <t>2,18; 2,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,82</t>
+          <t>2,36; 3,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 2,59</t>
+          <t>1,97; 2,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,88</t>
+          <t>2,23; 2,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,55</t>
+          <t>2,43; 3,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,36</t>
+          <t>2,23; 3,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,13</t>
+          <t>2,23; 3,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,11</t>
+          <t>2,33; 3,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,0</t>
+          <t>2,37; 3,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,35</t>
+          <t>2,45; 3,35</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,04</t>
+          <t>2,81; 4,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,37</t>
+          <t>2,55; 3,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,38</t>
+          <t>2,22; 3,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,37</t>
+          <t>2,59; 7,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,08</t>
+          <t>2,13; 3,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,49</t>
+          <t>1,98; 2,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,34</t>
+          <t>1,77; 2,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,95</t>
+          <t>2,16; 3,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,02</t>
+          <t>2,64; 4,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 2,91</t>
+          <t>2,38; 2,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,83</t>
+          <t>2,09; 2,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,22</t>
+          <t>2,5; 5,14</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,17</t>
+          <t>2,02; 3,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,69</t>
+          <t>2,13; 2,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,25</t>
+          <t>2,38; 3,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,53</t>
+          <t>2,32; 3,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,43</t>
+          <t>1,77; 2,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 2,6</t>
+          <t>2,0; 2,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,81</t>
+          <t>2,17; 2,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,99</t>
+          <t>2,65; 3,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,6</t>
+          <t>1,98; 2,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,52</t>
+          <t>2,13; 2,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,9</t>
+          <t>2,36; 2,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,5</t>
+          <t>2,58; 3,47</t>
         </is>
       </c>
     </row>
@@ -1276,27 +1276,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,27</t>
+          <t>2,51; 3,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,05</t>
+          <t>2,52; 3,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 2,79</t>
+          <t>2,37; 2,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,77</t>
+          <t>2,56; 3,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 2,37</t>
+          <t>2,04; 2,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 2,75</t>
+          <t>2,29; 2,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,11</t>
+          <t>2,55; 3,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,82</t>
+          <t>2,33; 2,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 2,78</t>
+          <t>2,45; 2,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 2,68</t>
+          <t>2,38; 2,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,3</t>
+          <t>2,64; 3,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q24D_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q24D_2-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,38</t>
+          <t>2,02; 3,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,55</t>
+          <t>2,52; 3,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,93</t>
+          <t>2,08; 2,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 2,68</t>
+          <t>2,04; 2,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,22</t>
+          <t>1,57; 2,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,9</t>
+          <t>2,4; 3,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,22</t>
+          <t>2,11; 3,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,81</t>
+          <t>2,1; 2,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 2,96</t>
+          <t>1,98; 3,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,35</t>
+          <t>2,58; 3,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,88</t>
+          <t>2,17; 2,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,62</t>
+          <t>2,15; 2,61</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,74</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>3,0</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,91</t>
+          <t>2,26; 3,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,83</t>
+          <t>2,24; 3,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,77</t>
+          <t>2,2; 2,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,76</t>
+          <t>2,51; 4,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,59</t>
+          <t>1,99; 2,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,87</t>
+          <t>2,25; 2,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,68</t>
+          <t>2,4; 3,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,27</t>
+          <t>2,3; 3,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,15</t>
+          <t>2,21; 3,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,11</t>
+          <t>2,32; 3,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,01</t>
+          <t>2,38; 2,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,35</t>
+          <t>2,54; 3,79</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>3,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>3,18</t>
         </is>
       </c>
     </row>
@@ -996,47 +996,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,95</t>
+          <t>2,8; 4,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,43</t>
+          <t>2,54; 3,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,29</t>
+          <t>2,18; 3,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,59</t>
+          <t>2,62; 7,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,13</t>
+          <t>2,18; 3,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,52</t>
+          <t>1,98; 2,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,36</t>
+          <t>1,76; 2,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,0</t>
+          <t>2,27; 3,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,02</t>
+          <t>2,69; 4,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 2,82</t>
+          <t>2,11; 2,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,14</t>
+          <t>2,57; 4,98</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>3,17</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,7</t>
+          <t>2,12; 2,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,28</t>
+          <t>2,4; 3,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,66</t>
+          <t>2,5; 4,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,37</t>
+          <t>1,79; 2,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,62</t>
+          <t>1,99; 2,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,78</t>
+          <t>2,18; 2,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,99</t>
+          <t>2,7; 4,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,62</t>
+          <t>1,98; 2,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,54</t>
+          <t>2,13; 2,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,88</t>
+          <t>2,36; 2,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,47</t>
+          <t>2,7; 3,77</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,98</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,25</t>
+          <t>2,51; 3,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,04</t>
+          <t>2,5; 3,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 2,76</t>
+          <t>2,38; 2,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 3,71</t>
+          <t>2,74; 4,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,39</t>
+          <t>2,03; 2,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 2,63</t>
+          <t>2,29; 2,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 2,77</t>
+          <t>2,32; 2,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,14</t>
+          <t>2,56; 3,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 2,8</t>
+          <t>2,35; 2,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 2,77</t>
+          <t>2,44; 2,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 2,7</t>
+          <t>2,39; 2,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 3,29</t>
+          <t>2,75; 3,43</t>
         </is>
       </c>
     </row>
